--- a/Data/Data.xlsx
+++ b/Data/Data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
     <t xml:space="preserve">Semester</t>
   </si>
@@ -31,19 +31,28 @@
     <t xml:space="preserve">Lektion</t>
   </si>
   <si>
+    <t xml:space="preserve">Anzahl Seiten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anzahl Wörter (Druckversion, geschätzt)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Anzahl benutzter Farben (Stift)</t>
   </si>
   <si>
     <t xml:space="preserve">Anzahl benutzter Farben (Marker)</t>
   </si>
   <si>
+    <t xml:space="preserve">Anzahl hervorgehobener Wörter</t>
+  </si>
+  <si>
     <t xml:space="preserve">Anteil handschriftlicher Notizen (geschätzt)</t>
   </si>
   <si>
     <t xml:space="preserve">Anzahl Zeichnungen (per Hand)</t>
   </si>
   <si>
-    <t xml:space="preserve">Anzahl Bilder</t>
+    <t xml:space="preserve">Anzahl Bilder (vorgefertigt)</t>
   </si>
   <si>
     <t xml:space="preserve">Anzahl hervorgehobener Elemente (besonders unterstrichen, umrandet, highlighted)</t>
@@ -55,7 +64,13 @@
     <t xml:space="preserve">Statistik</t>
   </si>
   <si>
+    <t xml:space="preserve">Merkmale und Häufigkeiten</t>
+  </si>
+  <si>
     <t xml:space="preserve">Statistik 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zufallsvariablen</t>
   </si>
   <si>
     <t xml:space="preserve">SS21</t>
@@ -157,15 +172,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:I8"/>
+  <dimension ref="A2:L8"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="28.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="36.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="68.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="26.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="28.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="26.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="36.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="26.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="68.54"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -196,47 +212,56 @@
       <c r="I2" s="0" t="s">
         <v>8</v>
       </c>
+      <c r="J2" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="0" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="0" t="n">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="0" t="n">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
